--- a/artfynd/A 73840-2021 artfynd.xlsx
+++ b/artfynd/A 73840-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 73840-2021 artfynd.xlsx
+++ b/artfynd/A 73840-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>111800</v>
       </c>
       <c r="B2" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459071.8315715379</v>
+        <v>459072</v>
       </c>
       <c r="R2" t="n">
-        <v>7098910.919237572</v>
+        <v>7098911</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2012-08-06</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-08-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1326196</v>
+        <v>343238</v>
       </c>
       <c r="B3" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>1205</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458876.9344068582</v>
+        <v>459143</v>
       </c>
       <c r="R3" t="n">
-        <v>7098919.187771652</v>
+        <v>7098779</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,19 +840,9 @@
           <t>2012-08-06</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2012-08-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1564062</v>
+        <v>1326196</v>
       </c>
       <c r="B4" t="n">
-        <v>89611</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5260</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Renvall</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459035.7403442755</v>
+        <v>458877</v>
       </c>
       <c r="R4" t="n">
-        <v>7098771.465666648</v>
+        <v>7098919</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -972,19 +937,9 @@
           <t>2012-08-06</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2012-08-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2025894</v>
+        <v>1564062</v>
       </c>
       <c r="B5" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92152</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>5260</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Postia lateritia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Renvall</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459089.1375283834</v>
+        <v>459036</v>
       </c>
       <c r="R5" t="n">
-        <v>7098890.953297094</v>
+        <v>7098771</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1084,19 +1034,9 @@
           <t>2012-08-06</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2012-08-06</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1993643</v>
+        <v>2059455</v>
       </c>
       <c r="B6" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459073.595158792</v>
+        <v>459130</v>
       </c>
       <c r="R6" t="n">
-        <v>7098877.99823804</v>
+        <v>7098846</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1196,19 +1131,9 @@
           <t>2012-08-06</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2012-08-06</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1993644</v>
+        <v>2059456</v>
       </c>
       <c r="B7" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459112.9886728762</v>
+        <v>459062</v>
       </c>
       <c r="R7" t="n">
-        <v>7098901.167511865</v>
+        <v>7098927</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1308,19 +1228,9 @@
           <t>2012-08-06</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2012-08-06</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2059456</v>
+        <v>1993643</v>
       </c>
       <c r="B8" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459061.9390906758</v>
+        <v>459074</v>
       </c>
       <c r="R8" t="n">
-        <v>7098926.840039256</v>
+        <v>7098878</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1420,19 +1325,9 @@
           <t>2012-08-06</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2012-08-06</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,37 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2071539</v>
+        <v>1993644</v>
       </c>
       <c r="B9" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458924.1629000314</v>
+        <v>459113</v>
       </c>
       <c r="R9" t="n">
-        <v>7098836.977600919</v>
+        <v>7098901</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1532,19 +1422,9 @@
           <t>2012-08-06</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2012-08-06</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,57 +1451,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>95398592</v>
+        <v>2071539</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Storrössjön, Jmt</t>
+          <t>Rössjön, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459096.1411074884</v>
+        <v>458924</v>
       </c>
       <c r="R10" t="n">
-        <v>7098755.319205364</v>
+        <v>7098837</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1645,22 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-08-06</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-08-06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-08-06</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-08-06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1669,76 +1530,66 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erik Söderhjelm</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erik Söderhjelm</t>
+          <t>Sebastian Acker</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>96374148</v>
+        <v>2025894</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Storrössjön /250 m NO/, Jmt</t>
+          <t>Rössjön, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459122.8716678865</v>
+        <v>459089</v>
       </c>
       <c r="R11" t="n">
-        <v>7098750.581842169</v>
+        <v>7098891</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1760,34 +1611,14 @@
           <t>Hotagen</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>Z-Kro-1714</t>
-        </is>
-      </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-08-06</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-08-06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-08-06</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Noterad på två platser med namn Storrössjön. Koordinat O1419770, N7101724 (±10m) och O1419715, N7101735 (±10m) RT90 2.5 gon. Summerat till Floraväkteriet.</t>
+          <t>2012-08-06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1796,22 +1627,337 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
+          <t>SCA Naturvärdesinventeringar</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>95398592</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Storrössjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>459096</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7098755</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-08-06</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-08-06</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>95398600</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Storrössjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>459151</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7098745</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2021-08-06</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2021-08-06</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>96374148</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Storrössjön /250 m NO/, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>459123</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7098751</v>
+      </c>
+      <c r="S14" t="n">
+        <v>50</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Z-Kro-1714</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2021-08-06</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2021-08-06</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Noterad på två platser med namn Storrössjön. Koordinat O1419770, N7101724 (±10m) och O1419715, N7101735 (±10m) RT90 2.5 gon. Summerat till Floraväkteriet.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
           <t>Lars-Åke Bäckström</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="AX14" t="inlineStr">
         <is>
           <t>Erik Söderhjelm</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr">
+      <c r="AY14" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>

--- a/artfynd/A 73840-2021 artfynd.xlsx
+++ b/artfynd/A 73840-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111800</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/343238</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1326196</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1564062</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2059455</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2059456</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1993643</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1993644</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2071539</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2025894</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1744,6 +1799,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95398592</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1846,6 +1906,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95398600</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1962,8 +2027,28 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96374148</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>